--- a/tasks/finalpool/fetch-wc-yf-financial-excel-word-email/groundtruth_workspace/Yf_Financial_Report.xlsx
+++ b/tasks/finalpool/fetch-wc-yf-financial-excel-word-email/groundtruth_workspace/Yf_Financial_Report.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,25 +440,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Product_Count</t>
+          <t>Our_Avg_Price</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Our_Avg_Price</t>
+          <t>Market_Avg_Price</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Sales</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Market_Avg_Price</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Price_Gap_Pct</t>
         </is>
@@ -471,18 +461,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>78.05</v>
       </c>
       <c r="C2" t="n">
-        <v>78.05</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>1553</v>
-      </c>
-      <c r="E2" t="n">
-        <v>74.15000000000001</v>
-      </c>
-      <c r="F2" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -493,18 +477,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>23.91</v>
       </c>
       <c r="C3" t="n">
-        <v>23.91</v>
+        <v>22.71</v>
       </c>
       <c r="D3" t="n">
-        <v>1041</v>
-      </c>
-      <c r="E3" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="F3" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -515,18 +493,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>61.13</v>
       </c>
       <c r="C4" t="n">
-        <v>61.13</v>
+        <v>58.07</v>
       </c>
       <c r="D4" t="n">
-        <v>2987</v>
-      </c>
-      <c r="E4" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="F4" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -537,18 +509,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>35.77</v>
       </c>
       <c r="C5" t="n">
-        <v>35.77</v>
+        <v>33.98</v>
       </c>
       <c r="D5" t="n">
-        <v>860</v>
-      </c>
-      <c r="E5" t="n">
-        <v>33.98</v>
-      </c>
-      <c r="F5" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -559,18 +525,12 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>304.9</v>
       </c>
       <c r="C6" t="n">
-        <v>304.9</v>
+        <v>289.65</v>
       </c>
       <c r="D6" t="n">
-        <v>1565</v>
-      </c>
-      <c r="E6" t="n">
-        <v>289.65</v>
-      </c>
-      <c r="F6" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -581,18 +541,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>60.69</v>
       </c>
       <c r="C7" t="n">
-        <v>60.69</v>
+        <v>57.66</v>
       </c>
       <c r="D7" t="n">
-        <v>411</v>
-      </c>
-      <c r="E7" t="n">
-        <v>57.66</v>
-      </c>
-      <c r="F7" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -663,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,11 +631,6 @@
           <t>Action</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -692,11 +641,6 @@
           <t>Price adjustment</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -705,11 +649,6 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>Marketing push</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Electronics</t>
         </is>
       </c>
     </row>

--- a/tasks/finalpool/fetch-wc-yf-financial-excel-word-email/groundtruth_workspace/Yf_Financial_Report.xlsx
+++ b/tasks/finalpool/fetch-wc-yf-financial-excel-word-email/groundtruth_workspace/Yf_Financial_Report.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,22 +531,6 @@
         <v>289.65</v>
       </c>
       <c r="D6" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Watches</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>60.69</v>
-      </c>
-      <c r="C7" t="n">
-        <v>57.66</v>
-      </c>
-      <c r="D7" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -583,7 +567,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
